--- a/data/hrm_sync_plan.xlsx
+++ b/data/hrm_sync_plan.xlsx
@@ -70,48 +70,48 @@
     <t>TU Extrusion</t>
   </si>
   <si>
+    <t>09/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>09/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>Thân Trọng Tuấn</t>
+  </si>
+  <si>
+    <t>Nguyễn Thành Thân</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng ca hỗ trợ kiểm kê tháng 9. </t>
+  </si>
+  <si>
+    <t>Chấp Nhận</t>
+  </si>
+  <si>
+    <t>02020390</t>
+  </si>
+  <si>
+    <t>Võ Thiên Tuế</t>
+  </si>
+  <si>
+    <t>19/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>19/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>Tăng ca sản xuất</t>
+  </si>
+  <si>
     <t>12/09/2026 06:00:00</t>
   </si>
   <si>
     <t>12/09/2026 14:00:00</t>
   </si>
   <si>
-    <t>Thân Trọng Tuấn</t>
-  </si>
-  <si>
-    <t>Nguyễn Thành Thân</t>
-  </si>
-  <si>
     <t>tăng ca sản xuất ca 1</t>
   </si>
   <si>
-    <t>Chấp Nhận</t>
-  </si>
-  <si>
-    <t>02020390</t>
-  </si>
-  <si>
-    <t>Võ Thiên Tuế</t>
-  </si>
-  <si>
-    <t>19/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>19/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>Tăng ca sản xuất</t>
-  </si>
-  <si>
-    <t>09/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>09/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tăng ca hỗ trợ kiểm kê tháng 9. </t>
-  </si>
-  <si>
     <t>12/09/2026 22:00:00</t>
   </si>
   <si>
@@ -145,6 +145,30 @@
     <t xml:space="preserve">tăng ca sản xuất.  ca2 </t>
   </si>
   <si>
+    <t>11/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>11/09/2026 16:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tăng ca lắp rack bobin x3. </t>
+  </si>
+  <si>
+    <t>02220255</t>
+  </si>
+  <si>
+    <t>Nguyễn Đức Sơn</t>
+  </si>
+  <si>
+    <t>14/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>14/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>tăng ca lắp rack xưởng 3</t>
+  </si>
+  <si>
     <t>01920589</t>
   </si>
   <si>
@@ -160,46 +184,94 @@
     <t xml:space="preserve">Hổ trợ sản xuất </t>
   </si>
   <si>
+    <t>10/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>10/09/2026 16:00:00</t>
+  </si>
+  <si>
+    <t>tăng ca lắp rack bobin</t>
+  </si>
+  <si>
+    <t>02020752</t>
+  </si>
+  <si>
+    <t>Nguyễn Chí Cường</t>
+  </si>
+  <si>
+    <t>Pulverize</t>
+  </si>
+  <si>
+    <t>12/09/2026 07:45:00</t>
+  </si>
+  <si>
+    <t>12/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tăng cường sản xuất </t>
+  </si>
+  <si>
+    <t>19/09/2026 07:45:00</t>
+  </si>
+  <si>
+    <t>19/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng ca hổ trợ sản xuất </t>
+  </si>
+  <si>
+    <t>02221908</t>
+  </si>
+  <si>
+    <t>Nguyễn Minh Hoàng</t>
+  </si>
+  <si>
+    <t>tăng ca hỗ trợ kiểm kê tháng 9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tăng ca hỗ trợ sản xuất </t>
+  </si>
+  <si>
+    <t>02022158</t>
+  </si>
+  <si>
+    <t>Bùi Lê Đức Minh</t>
+  </si>
+  <si>
+    <t>Hỗ trợ sản xuất(ca 3)</t>
+  </si>
+  <si>
     <t>19/09/2026 06:00:00</t>
   </si>
   <si>
     <t xml:space="preserve">tăng ca sản xuất.  ca1 </t>
   </si>
   <si>
-    <t>11/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>11/09/2026 16:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tăng ca lắp rack bobin x3. </t>
-  </si>
-  <si>
-    <t>10/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>10/09/2026 16:00:00</t>
-  </si>
-  <si>
-    <t>tăng ca lắp rack bobin</t>
-  </si>
-  <si>
-    <t>02020752</t>
-  </si>
-  <si>
-    <t>Nguyễn Chí Cường</t>
-  </si>
-  <si>
-    <t>Pulverize</t>
-  </si>
-  <si>
-    <t>12/09/2026 07:45:00</t>
-  </si>
-  <si>
-    <t>12/09/2026 16:30:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tăng cường sản xuất </t>
+    <t>07/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>07/09/2026 18:30:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tăng ca hổ trợ sản xuất </t>
+  </si>
+  <si>
+    <t>02224367</t>
+  </si>
+  <si>
+    <t>Ngô Minh Hiếu</t>
+  </si>
+  <si>
+    <t>Hỗ trợ sản xuất(ca 2)</t>
+  </si>
+  <si>
+    <t>tăng ca hỗ trợ lắp rack mobin</t>
+  </si>
+  <si>
+    <t>16/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>16/09/2026 16:00:00</t>
   </si>
   <si>
     <t>02021159</t>
@@ -211,46 +283,55 @@
     <t>tăng ca sản xuất ca 2</t>
   </si>
   <si>
-    <t>02220255</t>
-  </si>
-  <si>
-    <t>Nguyễn Đức Sơn</t>
-  </si>
-  <si>
-    <t>14/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>14/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>tăng ca lắp rack xưởng 3</t>
-  </si>
-  <si>
-    <t>02221908</t>
-  </si>
-  <si>
-    <t>Nguyễn Minh Hoàng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tăng ca hỗ trợ sản xuất </t>
-  </si>
-  <si>
-    <t>19/09/2026 07:45:00</t>
-  </si>
-  <si>
-    <t>19/09/2026 16:30:00</t>
-  </si>
-  <si>
-    <t>16/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>16/09/2026 16:00:00</t>
+    <t>Tăng ca hỗ trợ lắp rack mobin</t>
+  </si>
+  <si>
+    <t>18/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>18/09/2026 16:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lắp rack xưởng 3 </t>
   </si>
   <si>
     <t>tăng ca sản xuất : ca 1</t>
   </si>
   <si>
-    <t xml:space="preserve">tăng ca hổ trợ sản xuất </t>
+    <t>02227708</t>
+  </si>
+  <si>
+    <t>Phạm Việt Khải</t>
+  </si>
+  <si>
+    <t>Tăng ca hỗ trợ sản xuất (HC)</t>
+  </si>
+  <si>
+    <t>02224288</t>
+  </si>
+  <si>
+    <t>Võ Văn Dương</t>
+  </si>
+  <si>
+    <t>21/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>21/09/2026 16:00:00</t>
+  </si>
+  <si>
+    <t>tăng ca lắp rack bonbin</t>
+  </si>
+  <si>
+    <t>17/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>17/09/2026 18:00:00</t>
+  </si>
+  <si>
+    <t>15/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>15/09/2026 16:00:00</t>
   </si>
   <si>
     <t>02021645</t>
@@ -262,37 +343,13 @@
     <t xml:space="preserve">tăng ca sản xuất </t>
   </si>
   <si>
-    <t>15/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>15/09/2026 16:00:00</t>
-  </si>
-  <si>
-    <t>07/09/2026 16:30:00</t>
-  </si>
-  <si>
-    <t>07/09/2026 18:30:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tăng ca hổ trợ sản xuất </t>
-  </si>
-  <si>
     <t>tăng ca hỗ trợ sản xuất</t>
   </si>
   <si>
-    <t>18/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>18/09/2026 16:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lắp rack xưởng 3 </t>
-  </si>
-  <si>
-    <t>17/09/2026 16:30:00</t>
-  </si>
-  <si>
-    <t>17/09/2026 18:00:00</t>
+    <t>22/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>22/09/2026 16:00:00</t>
   </si>
   <si>
     <t>02243991</t>
@@ -310,6 +367,33 @@
     <t>lắp rack xưởng 3</t>
   </si>
   <si>
+    <t>02229894</t>
+  </si>
+  <si>
+    <t>Nguyễn Hữu Tài</t>
+  </si>
+  <si>
+    <t>tăng ca hỗ trợ sản xuất ca1</t>
+  </si>
+  <si>
+    <t>02020965</t>
+  </si>
+  <si>
+    <t>Hà Xuân Tiến</t>
+  </si>
+  <si>
+    <t>tăng ca hỗ trợ sản xuất, ca 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng ca hỗ trợ sản xuất ca3 </t>
+  </si>
+  <si>
+    <t>02325301</t>
+  </si>
+  <si>
+    <t>Cao Thế Mỹ</t>
+  </si>
+  <si>
     <t>02325295</t>
   </si>
   <si>
@@ -319,31 +403,31 @@
     <t xml:space="preserve">tăng ca  sản xuất  (ca 1)</t>
   </si>
   <si>
-    <t>02020965</t>
-  </si>
-  <si>
-    <t>Hà Xuân Tiến</t>
-  </si>
-  <si>
-    <t>tăng ca hỗ trợ sản xuất, ca 3</t>
-  </si>
-  <si>
     <t>02645278</t>
   </si>
   <si>
     <t>Moha Mad Nazid</t>
   </si>
   <si>
+    <t>03/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>03/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>tăng ca hổ trợ nghiền ca 3</t>
+  </si>
+  <si>
     <t>tăng ca hổ trợ nghiền ca 2</t>
   </si>
   <si>
-    <t>02022158</t>
-  </si>
-  <si>
-    <t>Bùi Lê Đức Minh</t>
-  </si>
-  <si>
-    <t>Hỗ trợ sản xuất(ca 3)</t>
+    <t>02645241</t>
+  </si>
+  <si>
+    <t>Nguyễn Đình Hoàng</t>
+  </si>
+  <si>
+    <t>hỗ trợ sản xuất(ca2)</t>
   </si>
   <si>
     <t>02222785</t>
@@ -355,37 +439,22 @@
     <t xml:space="preserve">tăng ca sản xuất ca 2 </t>
   </si>
   <si>
-    <t>03/09/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>03/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>tăng ca hổ trợ nghiền ca 3</t>
-  </si>
-  <si>
-    <t>02224367</t>
-  </si>
-  <si>
-    <t>Ngô Minh Hiếu</t>
-  </si>
-  <si>
-    <t>Hỗ trợ sản xuất(ca 2)</t>
-  </si>
-  <si>
-    <t>02227708</t>
-  </si>
-  <si>
-    <t>Phạm Việt Khải</t>
-  </si>
-  <si>
-    <t>Tăng ca hỗ trợ sản xuất (HC)</t>
-  </si>
-  <si>
-    <t>22/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>22/09/2026 16:00:00</t>
+    <t>17/09/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>hỗ trợ nghiền</t>
+  </si>
+  <si>
+    <t>16/09/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>hổ trợ nghiền</t>
+  </si>
+  <si>
+    <t>23/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>23/09/2026 15:30:00</t>
   </si>
   <si>
     <t>02241656</t>
@@ -397,118 +466,76 @@
     <t xml:space="preserve">tăng ca sản xuất ca3 </t>
   </si>
   <si>
+    <t>18/09/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>tăng ca sản xuất ca2</t>
+  </si>
+  <si>
+    <t>23/09/2026 16:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng ca lắp rack bonbin </t>
+  </si>
+  <si>
+    <t>Thay đổi nhân sự</t>
+  </si>
+  <si>
+    <t>Từ chối</t>
+  </si>
+  <si>
     <t>02325374</t>
   </si>
   <si>
     <t>Trương Văn Tình</t>
   </si>
   <si>
+    <t>Tăng ca sản xuất ( Ca 2 )</t>
+  </si>
+  <si>
+    <t>22/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>Tăng ca hỗ trợ nghiền ( Ca 1 )</t>
+  </si>
+  <si>
+    <t>15/09/2026 12:30:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tăng ca lắp rack xưởng 3 </t>
+  </si>
+  <si>
     <t>Tăng ca lắp rack xưởng 3</t>
   </si>
   <si>
-    <t>02645241</t>
-  </si>
-  <si>
-    <t>Nguyễn Đình Hoàng</t>
-  </si>
-  <si>
-    <t>17/09/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>hỗ trợ nghiền</t>
-  </si>
-  <si>
-    <t>Tăng ca sản xuất ( Ca 2 )</t>
-  </si>
-  <si>
-    <t>02229894</t>
-  </si>
-  <si>
-    <t>Nguyễn Hữu Tài</t>
-  </si>
-  <si>
-    <t>tăng ca hỗ trợ sản xuất ca1</t>
-  </si>
-  <si>
-    <t>tăng ca sản xuất ca2</t>
-  </si>
-  <si>
-    <t>tăng ca hỗ trợ kiểm kê tháng 9</t>
-  </si>
-  <si>
-    <t>tăng ca hỗ trợ lắp rack mobin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tăng ca hỗ trợ sản xuất ca3 </t>
-  </si>
-  <si>
-    <t>Tăng ca hỗ trợ lắp rack mobin</t>
-  </si>
-  <si>
-    <t>hỗ trợ sản xuất(ca2)</t>
-  </si>
-  <si>
-    <t>02224288</t>
-  </si>
-  <si>
-    <t>Võ Văn Dương</t>
-  </si>
-  <si>
-    <t>21/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>21/09/2026 16:00:00</t>
-  </si>
-  <si>
-    <t>tăng ca lắp rack bonbin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tăng ca lắp rack xưởng 3 </t>
-  </si>
-  <si>
-    <t>16/09/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>hổ trợ nghiền</t>
-  </si>
-  <si>
-    <t>Tăng ca hỗ trợ nghiền ( Ca 1 )</t>
-  </si>
-  <si>
-    <t>23/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>23/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>Chờ cấp trên gián tiếp</t>
-  </si>
-  <si>
-    <t>02325301</t>
-  </si>
-  <si>
-    <t>Cao Thế Mỹ</t>
-  </si>
-  <si>
-    <t>22/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>15/09/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>18/09/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>23/09/2026 16:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tăng ca lắp rack bonbin </t>
-  </si>
-  <si>
-    <t>Thay đổi nhân sự</t>
-  </si>
-  <si>
-    <t>Từ chối</t>
+    <t>01920862</t>
+  </si>
+  <si>
+    <t>Nguyễn Khắc Kiên</t>
+  </si>
+  <si>
+    <t>TĂNG CA SẢN XUẤT</t>
+  </si>
+  <si>
+    <t>02317843</t>
+  </si>
+  <si>
+    <t>Đinh Hoàng Phúc</t>
+  </si>
+  <si>
+    <t>T Extrusion</t>
+  </si>
+  <si>
+    <t>lắp Rack tại xưởng 3, chuẩn bị sản xuất line 21, 01</t>
+  </si>
+  <si>
+    <t>02516134</t>
+  </si>
+  <si>
+    <t>Ngô Xuân Nghĩa</t>
+  </si>
+  <si>
+    <t>Thực hiện dự án cải tiến</t>
   </si>
   <si>
     <t>02645269</t>
@@ -523,16 +550,67 @@
     <t>tăng ca hỗ trợ nghiền</t>
   </si>
   <si>
+    <t>thực hiện dự án cải tiến</t>
+  </si>
+  <si>
+    <t>02020497</t>
+  </si>
+  <si>
+    <t>Vũ Nhân Tài</t>
+  </si>
+  <si>
+    <t>Tăng ca hổ trợ sản xuất (HC)</t>
+  </si>
+  <si>
+    <t>lắp rack bobin tại xưởng 3</t>
+  </si>
+  <si>
+    <t>02411884</t>
+  </si>
+  <si>
+    <t>Phan Đình Lâm</t>
+  </si>
+  <si>
+    <t>Tăng ca vệ sinh máy PL24 test vật liệu mới.</t>
+  </si>
+  <si>
+    <t>Hỗ trợ lắp đặt rack mở rộng sản xuất.</t>
+  </si>
+  <si>
+    <t>22/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>22/09/2026 18:00:00</t>
+  </si>
+  <si>
+    <t>Lắp đặt rack Bobbin mở rộng sản xuất.</t>
+  </si>
+  <si>
+    <t>18/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>18/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>15/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>15/09/2026 18:00:00</t>
+  </si>
+  <si>
     <t>16/09/2026 20:30:00</t>
   </si>
   <si>
     <t>16/09/2026 22:00:00</t>
   </si>
   <si>
-    <t>18/09/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>18/09/2026 22:00:00</t>
+    <t>21/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>21/09/2026 18:00:00</t>
+  </si>
+  <si>
+    <t>Kiểm kê kho tháng 9.</t>
   </si>
   <si>
     <t>15/09/2026 20:30:00</t>
@@ -541,6 +619,21 @@
     <t>15/09/2026 22:00:00</t>
   </si>
   <si>
+    <t>02519007</t>
+  </si>
+  <si>
+    <t>Ninh Quang Trường</t>
+  </si>
+  <si>
+    <t>Hỗ trợ sản xuất</t>
+  </si>
+  <si>
+    <t>08/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>08/09/2026 19:30:00</t>
+  </si>
+  <si>
     <t>11/09/2026 15:30:00</t>
   </si>
   <si>
@@ -550,108 +643,12 @@
     <t>14/09/2026 22:00:00</t>
   </si>
   <si>
-    <t>02516134</t>
-  </si>
-  <si>
-    <t>Ngô Xuân Nghĩa</t>
-  </si>
-  <si>
-    <t>Thực hiện dự án cải tiến</t>
-  </si>
-  <si>
-    <t>thực hiện dự án cải tiến</t>
-  </si>
-  <si>
-    <t>02317843</t>
-  </si>
-  <si>
-    <t>Đinh Hoàng Phúc</t>
-  </si>
-  <si>
-    <t>T Extrusion</t>
-  </si>
-  <si>
-    <t>lắp Rack tại xưởng 3, chuẩn bị sản xuất line 21, 01</t>
-  </si>
-  <si>
-    <t>lắp rack bobin tại xưởng 3</t>
-  </si>
-  <si>
-    <t>02411884</t>
-  </si>
-  <si>
-    <t>Phan Đình Lâm</t>
-  </si>
-  <si>
-    <t>Hỗ trợ lắp đặt rack mở rộng sản xuất.</t>
-  </si>
-  <si>
-    <t>Tăng ca vệ sinh máy PL24 test vật liệu mới.</t>
-  </si>
-  <si>
-    <t>15/09/2026 16:30:00</t>
-  </si>
-  <si>
-    <t>15/09/2026 18:00:00</t>
-  </si>
-  <si>
-    <t>Lắp đặt rack Bobbin mở rộng sản xuất.</t>
-  </si>
-  <si>
-    <t>22/09/2026 16:30:00</t>
-  </si>
-  <si>
-    <t>22/09/2026 18:00:00</t>
-  </si>
-  <si>
-    <t>21/09/2026 16:30:00</t>
-  </si>
-  <si>
-    <t>21/09/2026 18:00:00</t>
-  </si>
-  <si>
-    <t>Kiểm kê kho tháng 9.</t>
-  </si>
-  <si>
-    <t>02519007</t>
-  </si>
-  <si>
-    <t>Ninh Quang Trường</t>
-  </si>
-  <si>
-    <t>Hỗ trợ sản xuất</t>
-  </si>
-  <si>
-    <t>08/09/2026 16:30:00</t>
-  </si>
-  <si>
-    <t>08/09/2026 19:30:00</t>
-  </si>
-  <si>
     <t>02619486</t>
   </si>
   <si>
     <t>Nguyễn Đức Huy</t>
   </si>
   <si>
-    <t>01920862</t>
-  </si>
-  <si>
-    <t>Nguyễn Khắc Kiên</t>
-  </si>
-  <si>
-    <t>TĂNG CA SẢN XUẤT</t>
-  </si>
-  <si>
-    <t>02020497</t>
-  </si>
-  <si>
-    <t>Vũ Nhân Tài</t>
-  </si>
-  <si>
-    <t>Tăng ca hổ trợ sản xuất (HC)</t>
-  </si>
-  <si>
     <t>02021131</t>
   </si>
   <si>
@@ -706,16 +703,22 @@
     <t>Trần Xuân Bắc</t>
   </si>
   <si>
+    <t xml:space="preserve">Tăng ca hỗ trợ nghiền </t>
+  </si>
+  <si>
+    <t>Hỗ trợ nghiền CA 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tăng ca thứ 7 </t>
+  </si>
+  <si>
     <t>Tăng ca hỗ trợ nghiền CA 3</t>
   </si>
   <si>
-    <t xml:space="preserve">Tăng ca thứ 7 </t>
-  </si>
-  <si>
-    <t>Hỗ trợ nghiền CA 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tăng ca hỗ trợ nghiền </t>
+    <t>17/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>17/09/2026 22:00:00</t>
   </si>
   <si>
     <t>Tăng ca hỗ trợ nghiền CA 1</t>
@@ -728,45 +731,6 @@
   </si>
   <si>
     <t>Hỗ trợ nghiền Ca1</t>
-  </si>
-  <si>
-    <t>17/09/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>17/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>02020947</t>
-  </si>
-  <si>
-    <t>Nguyễn Hoàng Duy</t>
-  </si>
-  <si>
-    <t>23/09/2026 16:30:00</t>
-  </si>
-  <si>
-    <t>23/09/2026 18:00:00</t>
-  </si>
-  <si>
-    <t>chuẩn bị kiểm kê</t>
-  </si>
-  <si>
-    <t>Chưa duyệt</t>
-  </si>
-  <si>
-    <t>02644075</t>
-  </si>
-  <si>
-    <t>Huỳnh Đại Nhân</t>
-  </si>
-  <si>
-    <t>23/09/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>23/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tăng cường sản xuất </t>
   </si>
 </sst>
 </file>
@@ -1249,7 +1213,7 @@
         <v>18</v>
       </c>
       <c r="G3" s="8">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H3" s="7" t="s">
         <v>19</v>
@@ -1321,7 +1285,7 @@
         <v>29</v>
       </c>
       <c r="G5" s="8">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H5" s="7" t="s">
         <v>19</v>
@@ -1459,7 +1423,7 @@
         <v>16</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>31</v>
@@ -1483,34 +1447,34 @@
     </row>
     <row r="10" s="2" customFormat="1">
       <c r="A10" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="F10" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="C10" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E10" s="8" t="s">
+      <c r="G10" s="8">
+        <v>120</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J10" s="7" t="s">
         <v>44</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="G10" s="8">
-        <v>180</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>46</v>
       </c>
       <c r="K10" s="7"/>
       <c r="L10" s="8" t="s">
@@ -1519,10 +1483,10 @@
     </row>
     <row r="11" s="2" customFormat="1">
       <c r="A11" s="7" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>15</v>
@@ -1534,10 +1498,10 @@
         <v>47</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="G11" s="8">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H11" s="7" t="s">
         <v>19</v>
@@ -1546,7 +1510,7 @@
         <v>20</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K11" s="7"/>
       <c r="L11" s="8" t="s">
@@ -1555,10 +1519,10 @@
     </row>
     <row r="12" s="2" customFormat="1">
       <c r="A12" s="7" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>15</v>
@@ -1567,13 +1531,13 @@
         <v>16</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G12" s="8">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="H12" s="7" t="s">
         <v>19</v>
@@ -1582,7 +1546,7 @@
         <v>20</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="K12" s="7"/>
       <c r="L12" s="8" t="s">
@@ -1603,10 +1567,10 @@
         <v>16</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G13" s="8">
         <v>120</v>
@@ -1618,7 +1582,7 @@
         <v>20</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="K13" s="7"/>
       <c r="L13" s="8" t="s">
@@ -1627,22 +1591,22 @@
     </row>
     <row r="14" s="2" customFormat="1">
       <c r="A14" s="7" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>57</v>
+        <v>16</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>58</v>
+        <v>29</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="G14" s="8">
         <v>480</v>
@@ -1654,7 +1618,7 @@
         <v>20</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="K14" s="7"/>
       <c r="L14" s="8" t="s">
@@ -1663,22 +1627,22 @@
     </row>
     <row r="15" s="2" customFormat="1">
       <c r="A15" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="E15" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="F15" s="8" t="s">
         <v>62</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>31</v>
       </c>
       <c r="G15" s="8">
         <v>480</v>
@@ -1699,10 +1663,10 @@
     </row>
     <row r="16" s="2" customFormat="1">
       <c r="A16" s="7" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>15</v>
@@ -1711,13 +1675,13 @@
         <v>16</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="G16" s="8">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H16" s="7" t="s">
         <v>19</v>
@@ -1726,7 +1690,7 @@
         <v>20</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="K16" s="7"/>
       <c r="L16" s="8" t="s">
@@ -1735,10 +1699,10 @@
     </row>
     <row r="17" s="2" customFormat="1">
       <c r="A17" s="7" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>15</v>
@@ -1747,10 +1711,10 @@
         <v>16</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>26</v>
+        <v>64</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="G17" s="8">
         <v>480</v>
@@ -1762,7 +1726,7 @@
         <v>20</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="K17" s="7"/>
       <c r="L17" s="8" t="s">
@@ -1771,10 +1735,10 @@
     </row>
     <row r="18" s="2" customFormat="1">
       <c r="A18" s="7" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>15</v>
@@ -1783,13 +1747,13 @@
         <v>16</v>
       </c>
       <c r="E18" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F18" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="F18" s="8" t="s">
-        <v>31</v>
-      </c>
       <c r="G18" s="8">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H18" s="7" t="s">
         <v>19</v>
@@ -1798,7 +1762,7 @@
         <v>20</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="K18" s="7"/>
       <c r="L18" s="8" t="s">
@@ -1807,22 +1771,22 @@
     </row>
     <row r="19" s="2" customFormat="1">
       <c r="A19" s="7" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>57</v>
+        <v>16</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>72</v>
+        <v>26</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>73</v>
+        <v>36</v>
       </c>
       <c r="G19" s="8">
         <v>480</v>
@@ -1834,7 +1798,7 @@
         <v>20</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="K19" s="7"/>
       <c r="L19" s="8" t="s">
@@ -1843,25 +1807,25 @@
     </row>
     <row r="20" s="2" customFormat="1">
       <c r="A20" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="E20" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="F20" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="C20" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="F20" s="8" t="s">
-        <v>75</v>
-      </c>
       <c r="G20" s="8">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="H20" s="7" t="s">
         <v>19</v>
@@ -1870,7 +1834,7 @@
         <v>20</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="K20" s="7"/>
       <c r="L20" s="8" t="s">
@@ -1879,10 +1843,10 @@
     </row>
     <row r="21" s="2" customFormat="1">
       <c r="A21" s="7" t="s">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="C21" s="7" t="s">
         <v>15</v>
@@ -1891,10 +1855,10 @@
         <v>16</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>58</v>
+        <v>31</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>59</v>
+        <v>32</v>
       </c>
       <c r="G21" s="8">
         <v>480</v>
@@ -1906,7 +1870,7 @@
         <v>20</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>46</v>
+        <v>73</v>
       </c>
       <c r="K21" s="7"/>
       <c r="L21" s="8" t="s">
@@ -1915,10 +1879,10 @@
     </row>
     <row r="22" s="2" customFormat="1">
       <c r="A22" s="7" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>15</v>
@@ -1927,10 +1891,10 @@
         <v>16</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G22" s="8">
         <v>480</v>
@@ -1942,7 +1906,7 @@
         <v>20</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="K22" s="7"/>
       <c r="L22" s="8" t="s">
@@ -1951,10 +1915,10 @@
     </row>
     <row r="23" s="2" customFormat="1">
       <c r="A23" s="7" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="C23" s="7" t="s">
         <v>15</v>
@@ -1963,7 +1927,7 @@
         <v>16</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="F23" s="8" t="s">
         <v>25</v>
@@ -1987,10 +1951,10 @@
     </row>
     <row r="24" s="2" customFormat="1">
       <c r="A24" s="7" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>15</v>
@@ -1999,10 +1963,10 @@
         <v>16</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>73</v>
+        <v>25</v>
       </c>
       <c r="G24" s="8">
         <v>480</v>
@@ -2014,7 +1978,7 @@
         <v>20</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="K24" s="7"/>
       <c r="L24" s="8" t="s">
@@ -2023,34 +1987,34 @@
     </row>
     <row r="25" s="2" customFormat="1">
       <c r="A25" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="G25" s="8">
+        <v>120</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I25" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J25" s="7" t="s">
         <v>78</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="F25" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="G25" s="8">
-        <v>480</v>
-      </c>
-      <c r="H25" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="I25" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="J25" s="7" t="s">
-        <v>80</v>
       </c>
       <c r="K25" s="7"/>
       <c r="L25" s="8" t="s">
@@ -2059,10 +2023,10 @@
     </row>
     <row r="26" s="2" customFormat="1">
       <c r="A26" s="7" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="C26" s="7" t="s">
         <v>15</v>
@@ -2071,13 +2035,13 @@
         <v>16</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>81</v>
+        <v>25</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>82</v>
+        <v>26</v>
       </c>
       <c r="G26" s="8">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="H26" s="7" t="s">
         <v>19</v>
@@ -2086,7 +2050,7 @@
         <v>20</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>68</v>
+        <v>33</v>
       </c>
       <c r="K26" s="7"/>
       <c r="L26" s="8" t="s">
@@ -2095,10 +2059,10 @@
     </row>
     <row r="27" s="2" customFormat="1">
       <c r="A27" s="7" t="s">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="C27" s="7" t="s">
         <v>15</v>
@@ -2107,13 +2071,13 @@
         <v>16</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>83</v>
+        <v>25</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>84</v>
+        <v>26</v>
       </c>
       <c r="G27" s="8">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="H27" s="7" t="s">
         <v>19</v>
@@ -2122,7 +2086,7 @@
         <v>20</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K27" s="7"/>
       <c r="L27" s="8" t="s">
@@ -2131,10 +2095,10 @@
     </row>
     <row r="28" s="2" customFormat="1">
       <c r="A28" s="7" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="C28" s="7" t="s">
         <v>15</v>
@@ -2143,13 +2107,13 @@
         <v>16</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="G28" s="8">
-        <v>480</v>
+        <v>120</v>
       </c>
       <c r="H28" s="7" t="s">
         <v>19</v>
@@ -2158,7 +2122,7 @@
         <v>20</v>
       </c>
       <c r="J28" s="7" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="K28" s="7"/>
       <c r="L28" s="8" t="s">
@@ -2167,10 +2131,10 @@
     </row>
     <row r="29" s="2" customFormat="1">
       <c r="A29" s="7" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="C29" s="7" t="s">
         <v>15</v>
@@ -2179,10 +2143,10 @@
         <v>16</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="G29" s="8">
         <v>120</v>
@@ -2194,7 +2158,7 @@
         <v>20</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>89</v>
+        <v>49</v>
       </c>
       <c r="K29" s="7"/>
       <c r="L29" s="8" t="s">
@@ -2203,10 +2167,10 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>42</v>
+        <v>85</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>43</v>
+        <v>86</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>15</v>
@@ -2215,13 +2179,13 @@
         <v>16</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>91</v>
+        <v>31</v>
       </c>
       <c r="G30" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>19</v>
@@ -2230,7 +2194,7 @@
         <v>20</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K30" s="3"/>
       <c r="L30" s="4" t="s">
@@ -2239,10 +2203,10 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>92</v>
+        <v>67</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>15</v>
@@ -2251,10 +2215,10 @@
         <v>16</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>94</v>
+        <v>55</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>95</v>
+        <v>56</v>
       </c>
       <c r="G31" s="4">
         <v>120</v>
@@ -2266,7 +2230,7 @@
         <v>20</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="K31" s="3"/>
       <c r="L31" s="4" t="s">
@@ -2275,10 +2239,10 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>97</v>
+        <v>45</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>98</v>
+        <v>46</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>15</v>
@@ -2287,13 +2251,13 @@
         <v>16</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>17</v>
+        <v>89</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="G32" s="4">
-        <v>480</v>
+        <v>120</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>19</v>
@@ -2302,7 +2266,7 @@
         <v>20</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="K32" s="3"/>
       <c r="L32" s="4" t="s">
@@ -2311,10 +2275,10 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>15</v>
@@ -2323,10 +2287,10 @@
         <v>16</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>26</v>
+        <v>74</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="G33" s="4">
         <v>480</v>
@@ -2338,7 +2302,7 @@
         <v>20</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="K33" s="3"/>
       <c r="L33" s="4" t="s">
@@ -2347,10 +2311,10 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>15</v>
@@ -2359,10 +2323,10 @@
         <v>16</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G34" s="4">
         <v>480</v>
@@ -2374,7 +2338,7 @@
         <v>20</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>105</v>
+        <v>33</v>
       </c>
       <c r="K34" s="3"/>
       <c r="L34" s="4" t="s">
@@ -2383,10 +2347,10 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>15</v>
@@ -2395,13 +2359,13 @@
         <v>16</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="G35" s="4">
-        <v>480</v>
+        <v>180</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>19</v>
@@ -2410,7 +2374,7 @@
         <v>20</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="K35" s="3"/>
       <c r="L35" s="4" t="s">
@@ -2419,10 +2383,10 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>15</v>
@@ -2431,13 +2395,13 @@
         <v>16</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>18</v>
+        <v>98</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>31</v>
+        <v>99</v>
       </c>
       <c r="G36" s="4">
-        <v>480</v>
+        <v>120</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>19</v>
@@ -2446,7 +2410,7 @@
         <v>20</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="K36" s="3"/>
       <c r="L36" s="4" t="s">
@@ -2455,10 +2419,10 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>103</v>
+        <v>50</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>104</v>
+        <v>51</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>15</v>
@@ -2467,10 +2431,10 @@
         <v>16</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="G37" s="4">
         <v>90</v>
@@ -2482,7 +2446,7 @@
         <v>20</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="K37" s="3"/>
       <c r="L37" s="4" t="s">
@@ -2491,10 +2455,10 @@
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>92</v>
+        <v>45</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>93</v>
+        <v>46</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>15</v>
@@ -2503,10 +2467,10 @@
         <v>16</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="G38" s="4">
         <v>120</v>
@@ -2518,7 +2482,7 @@
         <v>20</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>96</v>
+        <v>49</v>
       </c>
       <c r="K38" s="3"/>
       <c r="L38" s="4" t="s">
@@ -2527,10 +2491,10 @@
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>15</v>
@@ -2539,10 +2503,10 @@
         <v>16</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="G39" s="4">
         <v>480</v>
@@ -2554,7 +2518,7 @@
         <v>20</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="K39" s="3"/>
       <c r="L39" s="4" t="s">
@@ -2563,10 +2527,10 @@
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>15</v>
@@ -2575,10 +2539,10 @@
         <v>16</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G40" s="4">
         <v>480</v>
@@ -2590,7 +2554,7 @@
         <v>20</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>33</v>
+        <v>108</v>
       </c>
       <c r="K40" s="3"/>
       <c r="L40" s="4" t="s">
@@ -2599,10 +2563,10 @@
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>115</v>
+        <v>79</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>15</v>
@@ -2611,13 +2575,13 @@
         <v>16</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>25</v>
+        <v>109</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>26</v>
+        <v>110</v>
       </c>
       <c r="G41" s="4">
-        <v>480</v>
+        <v>120</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>19</v>
@@ -2626,7 +2590,7 @@
         <v>20</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="K41" s="3"/>
       <c r="L41" s="4" t="s">
@@ -2635,10 +2599,10 @@
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>15</v>
@@ -2647,10 +2611,10 @@
         <v>16</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="G42" s="4">
         <v>480</v>
@@ -2662,7 +2626,7 @@
         <v>20</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>117</v>
+        <v>95</v>
       </c>
       <c r="K42" s="3"/>
       <c r="L42" s="4" t="s">
@@ -2671,10 +2635,10 @@
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>15</v>
@@ -2683,13 +2647,13 @@
         <v>16</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>44</v>
+        <v>113</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>45</v>
+        <v>114</v>
       </c>
       <c r="G43" s="4">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>19</v>
@@ -2698,7 +2662,7 @@
         <v>20</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="K43" s="3"/>
       <c r="L43" s="4" t="s">
@@ -2707,34 +2671,34 @@
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G44" s="4">
+        <v>480</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J44" s="3" t="s">
         <v>118</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E44" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="F44" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="G44" s="4">
-        <v>480</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>120</v>
       </c>
       <c r="K44" s="3"/>
       <c r="L44" s="4" t="s">
@@ -2743,10 +2707,10 @@
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>92</v>
+        <v>119</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>93</v>
+        <v>120</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>15</v>
@@ -2755,10 +2719,10 @@
         <v>16</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="G45" s="4">
         <v>480</v>
@@ -2770,7 +2734,7 @@
         <v>20</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>21</v>
+        <v>121</v>
       </c>
       <c r="K45" s="3"/>
       <c r="L45" s="4" t="s">
@@ -2779,10 +2743,10 @@
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>116</v>
+        <v>97</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>15</v>
@@ -2791,13 +2755,13 @@
         <v>16</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>121</v>
+        <v>31</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>122</v>
+        <v>32</v>
       </c>
       <c r="G46" s="4">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>19</v>
@@ -2806,7 +2770,7 @@
         <v>20</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>54</v>
+        <v>107</v>
       </c>
       <c r="K46" s="3"/>
       <c r="L46" s="4" t="s">
@@ -2815,10 +2779,10 @@
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>15</v>
@@ -2827,10 +2791,10 @@
         <v>16</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G47" s="4">
         <v>480</v>
@@ -2842,7 +2806,7 @@
         <v>20</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="K47" s="3"/>
       <c r="L47" s="4" t="s">
@@ -2851,10 +2815,10 @@
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>69</v>
+        <v>123</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>15</v>
@@ -2863,10 +2827,10 @@
         <v>16</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>17</v>
+        <v>74</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="G48" s="4">
         <v>480</v>
@@ -2878,7 +2842,7 @@
         <v>20</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>71</v>
+        <v>107</v>
       </c>
       <c r="K48" s="3"/>
       <c r="L48" s="4" t="s">
@@ -2887,10 +2851,10 @@
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>15</v>
@@ -2899,10 +2863,10 @@
         <v>16</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>72</v>
+        <v>28</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="G49" s="4">
         <v>480</v>
@@ -2914,7 +2878,7 @@
         <v>20</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="K49" s="3"/>
       <c r="L49" s="4" t="s">
@@ -2923,10 +2887,10 @@
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>15</v>
@@ -2935,10 +2899,10 @@
         <v>16</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>66</v>
+        <v>130</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>67</v>
+        <v>131</v>
       </c>
       <c r="G50" s="4">
         <v>90</v>
@@ -2950,7 +2914,7 @@
         <v>20</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="K50" s="3"/>
       <c r="L50" s="4" t="s">
@@ -2959,10 +2923,10 @@
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="C51" s="3" t="s">
         <v>15</v>
@@ -2971,13 +2935,13 @@
         <v>16</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>131</v>
+        <v>89</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G51" s="4">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>19</v>
@@ -2986,7 +2950,7 @@
         <v>20</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="K51" s="3"/>
       <c r="L51" s="4" t="s">
@@ -2995,10 +2959,10 @@
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>126</v>
+        <v>93</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>127</v>
+        <v>94</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>15</v>
@@ -3007,10 +2971,10 @@
         <v>16</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>18</v>
+        <v>64</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>31</v>
+        <v>65</v>
       </c>
       <c r="G52" s="4">
         <v>480</v>
@@ -3022,7 +2986,7 @@
         <v>20</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>133</v>
+        <v>95</v>
       </c>
       <c r="K52" s="3"/>
       <c r="L52" s="4" t="s">
@@ -3031,10 +2995,10 @@
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="C53" s="3" t="s">
         <v>15</v>
@@ -3043,10 +3007,10 @@
         <v>16</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="G53" s="4">
         <v>480</v>
@@ -3058,7 +3022,7 @@
         <v>20</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="K53" s="3"/>
       <c r="L53" s="4" t="s">
@@ -3067,10 +3031,10 @@
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>15</v>
@@ -3094,7 +3058,7 @@
         <v>20</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="K54" s="3"/>
       <c r="L54" s="4" t="s">
@@ -3103,10 +3067,10 @@
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>69</v>
+        <v>111</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>70</v>
+        <v>112</v>
       </c>
       <c r="C55" s="3" t="s">
         <v>15</v>
@@ -3115,13 +3079,13 @@
         <v>16</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>28</v>
+        <v>74</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G55" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>19</v>
@@ -3130,7 +3094,7 @@
         <v>20</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>138</v>
+        <v>30</v>
       </c>
       <c r="K55" s="3"/>
       <c r="L55" s="4" t="s">
@@ -3139,10 +3103,10 @@
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>69</v>
+        <v>96</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>70</v>
+        <v>97</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>15</v>
@@ -3151,13 +3115,13 @@
         <v>16</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="G56" s="4">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="H56" s="3" t="s">
         <v>19</v>
@@ -3166,7 +3130,7 @@
         <v>20</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>139</v>
+        <v>107</v>
       </c>
       <c r="K56" s="3"/>
       <c r="L56" s="4" t="s">
@@ -3175,10 +3139,10 @@
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>15</v>
@@ -3187,10 +3151,10 @@
         <v>16</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G57" s="4">
         <v>480</v>
@@ -3202,7 +3166,7 @@
         <v>20</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K57" s="3"/>
       <c r="L57" s="4" t="s">
@@ -3211,10 +3175,10 @@
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>69</v>
+        <v>134</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>70</v>
+        <v>135</v>
       </c>
       <c r="C58" s="3" t="s">
         <v>15</v>
@@ -3223,13 +3187,13 @@
         <v>16</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>52</v>
+        <v>140</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>53</v>
+        <v>113</v>
       </c>
       <c r="G58" s="4">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>19</v>
@@ -3247,10 +3211,10 @@
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="C59" s="3" t="s">
         <v>15</v>
@@ -3259,11 +3223,11 @@
         <v>16</v>
       </c>
       <c r="E59" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="F59" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="F59" s="4" t="s">
-        <v>26</v>
-      </c>
       <c r="G59" s="4">
         <v>480</v>
       </c>
@@ -3274,7 +3238,7 @@
         <v>20</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>142</v>
+        <v>30</v>
       </c>
       <c r="K59" s="3"/>
       <c r="L59" s="4" t="s">
@@ -3283,34 +3247,34 @@
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E60" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="F60" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="G60" s="4">
+        <v>90</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J60" s="3" t="s">
         <v>143</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D60" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E60" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="F60" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="G60" s="4">
-        <v>120</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="I60" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J60" s="3" t="s">
-        <v>147</v>
       </c>
       <c r="K60" s="3"/>
       <c r="L60" s="4" t="s">
@@ -3319,10 +3283,10 @@
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="C61" s="3" t="s">
         <v>15</v>
@@ -3331,13 +3295,13 @@
         <v>16</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>94</v>
+        <v>144</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>95</v>
+        <v>145</v>
       </c>
       <c r="G61" s="4">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="H61" s="3" t="s">
         <v>19</v>
@@ -3346,7 +3310,7 @@
         <v>20</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="K61" s="3"/>
       <c r="L61" s="4" t="s">
@@ -3355,10 +3319,10 @@
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>130</v>
+        <v>147</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>15</v>
@@ -3367,13 +3331,13 @@
         <v>16</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>149</v>
+        <v>31</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>74</v>
+        <v>32</v>
       </c>
       <c r="G62" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>19</v>
@@ -3382,7 +3346,7 @@
         <v>20</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="K62" s="3"/>
       <c r="L62" s="4" t="s">
@@ -3391,10 +3355,10 @@
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>15</v>
@@ -3403,13 +3367,13 @@
         <v>16</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>31</v>
+        <v>149</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>32</v>
+        <v>89</v>
       </c>
       <c r="G63" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H63" s="3" t="s">
         <v>19</v>
@@ -3418,7 +3382,7 @@
         <v>20</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>80</v>
+        <v>141</v>
       </c>
       <c r="K63" s="3"/>
       <c r="L63" s="4" t="s">
@@ -3427,10 +3391,10 @@
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>126</v>
+        <v>146</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>15</v>
@@ -3439,10 +3403,10 @@
         <v>16</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G64" s="4">
         <v>480</v>
@@ -3454,7 +3418,7 @@
         <v>20</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K64" s="3"/>
       <c r="L64" s="4" t="s">
@@ -3463,10 +3427,10 @@
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>129</v>
+        <v>96</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>130</v>
+        <v>97</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>15</v>
@@ -3475,24 +3439,26 @@
         <v>16</v>
       </c>
       <c r="E65" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="F65" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="G65" s="4">
+        <v>120</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I65" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J65" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="F65" s="4" t="s">
+      <c r="K65" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="G65" s="4">
-        <v>90</v>
-      </c>
-      <c r="H65" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="I65" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J65" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="K65" s="3"/>
       <c r="L65" s="4" t="s">
         <v>154</v>
       </c>
@@ -3511,10 +3477,10 @@
         <v>16</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="G66" s="4">
         <v>480</v>
@@ -3526,7 +3492,7 @@
         <v>20</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>80</v>
+        <v>157</v>
       </c>
       <c r="K66" s="3"/>
       <c r="L66" s="4" t="s">
@@ -3535,10 +3501,10 @@
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>143</v>
+        <v>96</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>144</v>
+        <v>97</v>
       </c>
       <c r="C67" s="3" t="s">
         <v>15</v>
@@ -3547,13 +3513,13 @@
         <v>16</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>25</v>
+        <v>109</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>26</v>
+        <v>110</v>
       </c>
       <c r="G67" s="4">
-        <v>480</v>
+        <v>120</v>
       </c>
       <c r="H67" s="3" t="s">
         <v>19</v>
@@ -3562,7 +3528,7 @@
         <v>20</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>80</v>
+        <v>152</v>
       </c>
       <c r="K67" s="3"/>
       <c r="L67" s="4" t="s">
@@ -3571,10 +3537,10 @@
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="C68" s="3" t="s">
         <v>15</v>
@@ -3583,10 +3549,10 @@
         <v>16</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G68" s="4">
         <v>90</v>
@@ -3598,7 +3564,7 @@
         <v>20</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="K68" s="3"/>
       <c r="L68" s="4" t="s">
@@ -3607,10 +3573,10 @@
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>129</v>
+        <v>155</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>130</v>
+        <v>156</v>
       </c>
       <c r="C69" s="3" t="s">
         <v>15</v>
@@ -3619,13 +3585,13 @@
         <v>16</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>158</v>
+        <v>74</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>81</v>
+        <v>25</v>
       </c>
       <c r="G69" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H69" s="3" t="s">
         <v>19</v>
@@ -3634,7 +3600,7 @@
         <v>20</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>132</v>
+        <v>159</v>
       </c>
       <c r="K69" s="3"/>
       <c r="L69" s="4" t="s">
@@ -3643,10 +3609,10 @@
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>15</v>
@@ -3655,10 +3621,10 @@
         <v>16</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="G70" s="4">
         <v>90</v>
@@ -3670,7 +3636,7 @@
         <v>20</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="K70" s="3"/>
       <c r="L70" s="4" t="s">
@@ -3679,10 +3645,10 @@
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="C71" s="3" t="s">
         <v>15</v>
@@ -3691,10 +3657,10 @@
         <v>16</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>152</v>
+        <v>113</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>160</v>
+        <v>114</v>
       </c>
       <c r="G71" s="4">
         <v>120</v>
@@ -3708,19 +3674,17 @@
       <c r="J71" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="K71" s="3" t="s">
-        <v>162</v>
-      </c>
+      <c r="K71" s="3"/>
       <c r="L71" s="4" t="s">
-        <v>163</v>
+        <v>22</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="C72" s="3" t="s">
         <v>15</v>
@@ -3729,10 +3693,10 @@
         <v>16</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>121</v>
+        <v>83</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>122</v>
+        <v>84</v>
       </c>
       <c r="G72" s="4">
         <v>120</v>
@@ -3753,10 +3717,10 @@
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="C73" s="3" t="s">
         <v>15</v>
@@ -3765,13 +3729,13 @@
         <v>16</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>52</v>
+        <v>103</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>166</v>
+        <v>104</v>
       </c>
       <c r="G73" s="4">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="H73" s="3" t="s">
         <v>19</v>
@@ -3780,7 +3744,7 @@
         <v>20</v>
       </c>
       <c r="J73" s="3" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="K73" s="3"/>
       <c r="L73" s="4" t="s">
@@ -3789,10 +3753,10 @@
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>15</v>
@@ -3801,13 +3765,13 @@
         <v>16</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="G74" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H74" s="3" t="s">
         <v>19</v>
@@ -3816,7 +3780,7 @@
         <v>20</v>
       </c>
       <c r="J74" s="3" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="K74" s="3"/>
       <c r="L74" s="4" t="s">
@@ -3825,34 +3789,34 @@
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="B75" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="B75" s="3" t="s">
+      <c r="C75" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E75" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F75" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G75" s="4">
+        <v>480</v>
+      </c>
+      <c r="H75" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I75" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J75" s="3" t="s">
         <v>165</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D75" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E75" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="F75" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="G75" s="4">
-        <v>90</v>
-      </c>
-      <c r="H75" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="I75" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J75" s="3" t="s">
-        <v>167</v>
       </c>
       <c r="K75" s="3"/>
       <c r="L75" s="4" t="s">
@@ -3861,25 +3825,25 @@
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C76" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>16</v>
+        <v>168</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="G76" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H76" s="3" t="s">
         <v>19</v>
@@ -3888,7 +3852,7 @@
         <v>20</v>
       </c>
       <c r="J76" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="K76" s="3"/>
       <c r="L76" s="4" t="s">
@@ -3897,34 +3861,34 @@
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="B77" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="B77" s="3" t="s">
+      <c r="C77" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E77" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="F77" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G77" s="4">
+        <v>480</v>
+      </c>
+      <c r="H77" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I77" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J77" s="3" t="s">
         <v>165</v>
-      </c>
-      <c r="C77" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D77" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E77" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F77" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="G77" s="4">
-        <v>480</v>
-      </c>
-      <c r="H77" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="I77" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J77" s="3" t="s">
-        <v>167</v>
       </c>
       <c r="K77" s="3"/>
       <c r="L77" s="4" t="s">
@@ -3933,10 +3897,10 @@
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="C78" s="3" t="s">
         <v>15</v>
@@ -3945,13 +3909,13 @@
         <v>16</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>170</v>
+        <v>64</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>171</v>
+        <v>65</v>
       </c>
       <c r="G78" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H78" s="3" t="s">
         <v>19</v>
@@ -3960,7 +3924,7 @@
         <v>20</v>
       </c>
       <c r="J78" s="3" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="K78" s="3"/>
       <c r="L78" s="4" t="s">
@@ -3969,10 +3933,10 @@
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="C79" s="3" t="s">
         <v>15</v>
@@ -3981,10 +3945,10 @@
         <v>16</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>172</v>
+        <v>55</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G79" s="4">
         <v>90</v>
@@ -3996,7 +3960,7 @@
         <v>20</v>
       </c>
       <c r="J79" s="3" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="K79" s="3"/>
       <c r="L79" s="4" t="s">
@@ -4005,10 +3969,10 @@
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="C80" s="3" t="s">
         <v>15</v>
@@ -4017,13 +3981,13 @@
         <v>16</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>174</v>
+        <v>62</v>
       </c>
       <c r="G80" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H80" s="3" t="s">
         <v>19</v>
@@ -4032,7 +3996,7 @@
         <v>20</v>
       </c>
       <c r="J80" s="3" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="K80" s="3"/>
       <c r="L80" s="4" t="s">
@@ -4041,10 +4005,10 @@
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>126</v>
+        <v>178</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>127</v>
+        <v>179</v>
       </c>
       <c r="C81" s="3" t="s">
         <v>15</v>
@@ -4053,13 +4017,13 @@
         <v>16</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="G81" s="4">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="H81" s="3" t="s">
         <v>19</v>
@@ -4068,7 +4032,7 @@
         <v>20</v>
       </c>
       <c r="J81" s="3" t="s">
-        <v>148</v>
+        <v>180</v>
       </c>
       <c r="K81" s="3"/>
       <c r="L81" s="4" t="s">
@@ -4077,10 +4041,10 @@
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="C82" s="3" t="s">
         <v>15</v>
@@ -4089,10 +4053,10 @@
         <v>16</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>175</v>
+        <v>17</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>176</v>
+        <v>18</v>
       </c>
       <c r="G82" s="4">
         <v>90</v>
@@ -4104,7 +4068,7 @@
         <v>20</v>
       </c>
       <c r="J82" s="3" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="K82" s="3"/>
       <c r="L82" s="4" t="s">
@@ -4113,22 +4077,22 @@
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="C83" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>16</v>
+        <v>168</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="G83" s="4">
         <v>480</v>
@@ -4140,7 +4104,7 @@
         <v>20</v>
       </c>
       <c r="J83" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="K83" s="3"/>
       <c r="L83" s="4" t="s">
@@ -4149,10 +4113,10 @@
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>126</v>
+        <v>182</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>127</v>
+        <v>183</v>
       </c>
       <c r="C84" s="3" t="s">
         <v>15</v>
@@ -4161,13 +4125,13 @@
         <v>16</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>82</v>
+        <v>53</v>
       </c>
       <c r="G84" s="4">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="H84" s="3" t="s">
         <v>19</v>
@@ -4176,7 +4140,7 @@
         <v>20</v>
       </c>
       <c r="J84" s="3" t="s">
-        <v>148</v>
+        <v>184</v>
       </c>
       <c r="K84" s="3"/>
       <c r="L84" s="4" t="s">
@@ -4185,10 +4149,10 @@
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="C85" s="3" t="s">
         <v>15</v>
@@ -4197,10 +4161,10 @@
         <v>16</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="G85" s="4">
         <v>480</v>
@@ -4212,7 +4176,7 @@
         <v>20</v>
       </c>
       <c r="J85" s="3" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="K85" s="3"/>
       <c r="L85" s="4" t="s">
@@ -4221,25 +4185,25 @@
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C86" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>183</v>
+        <v>16</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>58</v>
+        <v>186</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>59</v>
+        <v>187</v>
       </c>
       <c r="G86" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H86" s="3" t="s">
         <v>19</v>
@@ -4248,7 +4212,7 @@
         <v>20</v>
       </c>
       <c r="J86" s="3" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="K86" s="3"/>
       <c r="L86" s="4" t="s">
@@ -4257,22 +4221,22 @@
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="C87" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>183</v>
+        <v>16</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>72</v>
+        <v>28</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="G87" s="4">
         <v>480</v>
@@ -4284,7 +4248,7 @@
         <v>20</v>
       </c>
       <c r="J87" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="K87" s="3"/>
       <c r="L87" s="4" t="s">
@@ -4293,10 +4257,10 @@
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="C88" s="3" t="s">
         <v>15</v>
@@ -4305,10 +4269,10 @@
         <v>16</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>72</v>
+        <v>26</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>73</v>
+        <v>36</v>
       </c>
       <c r="G88" s="4">
         <v>480</v>
@@ -4320,7 +4284,7 @@
         <v>20</v>
       </c>
       <c r="J88" s="3" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="K88" s="3"/>
       <c r="L88" s="4" t="s">
@@ -4329,10 +4293,10 @@
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="C89" s="3" t="s">
         <v>15</v>
@@ -4341,13 +4305,13 @@
         <v>16</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>44</v>
+        <v>189</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>45</v>
+        <v>190</v>
       </c>
       <c r="G89" s="4">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="H89" s="3" t="s">
         <v>19</v>
@@ -4356,7 +4320,7 @@
         <v>20</v>
       </c>
       <c r="J89" s="3" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="K89" s="3"/>
       <c r="L89" s="4" t="s">
@@ -4365,10 +4329,10 @@
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C90" s="3" t="s">
         <v>15</v>
@@ -4377,10 +4341,10 @@
         <v>16</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G90" s="4">
         <v>90</v>
@@ -4392,7 +4356,7 @@
         <v>20</v>
       </c>
       <c r="J90" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="K90" s="3"/>
       <c r="L90" s="4" t="s">
@@ -4401,10 +4365,10 @@
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="C91" s="3" t="s">
         <v>15</v>
@@ -4428,7 +4392,7 @@
         <v>20</v>
       </c>
       <c r="J91" s="3" t="s">
-        <v>192</v>
+        <v>176</v>
       </c>
       <c r="K91" s="3"/>
       <c r="L91" s="4" t="s">
@@ -4437,10 +4401,10 @@
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C92" s="3" t="s">
         <v>15</v>
@@ -4473,22 +4437,22 @@
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E93" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="B93" s="3" t="s">
+      <c r="F93" s="4" t="s">
         <v>199</v>
-      </c>
-      <c r="C93" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D93" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E93" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="F93" s="4" t="s">
-        <v>91</v>
       </c>
       <c r="G93" s="4">
         <v>90</v>
@@ -4500,7 +4464,7 @@
         <v>20</v>
       </c>
       <c r="J93" s="3" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="K93" s="3"/>
       <c r="L93" s="4" t="s">
@@ -4509,10 +4473,10 @@
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C94" s="3" t="s">
         <v>15</v>
@@ -4521,10 +4485,10 @@
         <v>16</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G94" s="4">
         <v>480</v>
@@ -4536,7 +4500,7 @@
         <v>20</v>
       </c>
       <c r="J94" s="3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="K94" s="3"/>
       <c r="L94" s="4" t="s">
@@ -4545,10 +4509,10 @@
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C95" s="3" t="s">
         <v>15</v>
@@ -4557,13 +4521,13 @@
         <v>16</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="G95" s="4">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="H95" s="3" t="s">
         <v>19</v>
@@ -4572,7 +4536,7 @@
         <v>20</v>
       </c>
       <c r="J95" s="3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="K95" s="3"/>
       <c r="L95" s="4" t="s">
@@ -4581,10 +4545,10 @@
     </row>
     <row r="96">
       <c r="A96" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C96" s="3" t="s">
         <v>15</v>
@@ -4593,10 +4557,10 @@
         <v>16</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="G96" s="4">
         <v>90</v>
@@ -4608,7 +4572,7 @@
         <v>20</v>
       </c>
       <c r="J96" s="3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="K96" s="3"/>
       <c r="L96" s="4" t="s">
@@ -4617,10 +4581,10 @@
     </row>
     <row r="97">
       <c r="A97" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C97" s="3" t="s">
         <v>15</v>
@@ -4629,22 +4593,22 @@
         <v>16</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="F97" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="G97" s="4">
+        <v>90</v>
+      </c>
+      <c r="H97" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I97" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J97" s="3" t="s">
         <v>202</v>
-      </c>
-      <c r="G97" s="4">
-        <v>180</v>
-      </c>
-      <c r="H97" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="I97" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J97" s="3" t="s">
-        <v>200</v>
       </c>
       <c r="K97" s="3"/>
       <c r="L97" s="4" t="s">
@@ -4653,10 +4617,10 @@
     </row>
     <row r="98">
       <c r="A98" s="3" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C98" s="3" t="s">
         <v>15</v>
@@ -4665,13 +4629,13 @@
         <v>16</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="G98" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H98" s="3" t="s">
         <v>19</v>
@@ -4680,7 +4644,7 @@
         <v>20</v>
       </c>
       <c r="J98" s="3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="K98" s="3"/>
       <c r="L98" s="4" t="s">
@@ -4689,25 +4653,25 @@
     </row>
     <row r="99">
       <c r="A99" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E99" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F99" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="B99" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="C99" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D99" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E99" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F99" s="4" t="s">
-        <v>31</v>
-      </c>
       <c r="G99" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H99" s="3" t="s">
         <v>19</v>
@@ -4716,7 +4680,7 @@
         <v>20</v>
       </c>
       <c r="J99" s="3" t="s">
-        <v>207</v>
+        <v>176</v>
       </c>
       <c r="K99" s="3"/>
       <c r="L99" s="4" t="s">
@@ -4725,25 +4689,25 @@
     </row>
     <row r="100">
       <c r="A100" s="3" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="B100" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E100" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="C100" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D100" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E100" s="4" t="s">
-        <v>47</v>
-      </c>
       <c r="F100" s="4" t="s">
-        <v>25</v>
+        <v>207</v>
       </c>
       <c r="G100" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H100" s="3" t="s">
         <v>19</v>
@@ -4752,7 +4716,7 @@
         <v>20</v>
       </c>
       <c r="J100" s="3" t="s">
-        <v>207</v>
+        <v>176</v>
       </c>
       <c r="K100" s="3"/>
       <c r="L100" s="4" t="s">
@@ -4773,10 +4737,10 @@
         <v>16</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="G101" s="4">
         <v>480</v>
@@ -4788,7 +4752,7 @@
         <v>20</v>
       </c>
       <c r="J101" s="3" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="K101" s="3"/>
       <c r="L101" s="4" t="s">
@@ -4797,10 +4761,10 @@
     </row>
     <row r="102">
       <c r="A102" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B102" s="3" t="s">
         <v>211</v>
-      </c>
-      <c r="B102" s="3" t="s">
-        <v>212</v>
       </c>
       <c r="C102" s="3" t="s">
         <v>15</v>
@@ -4824,7 +4788,7 @@
         <v>20</v>
       </c>
       <c r="J102" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="K102" s="3"/>
       <c r="L102" s="4" t="s">
@@ -4833,11 +4797,11 @@
     </row>
     <row r="103">
       <c r="A103" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B103" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="B103" s="3" t="s">
-        <v>215</v>
-      </c>
       <c r="C103" s="3" t="s">
         <v>15</v>
       </c>
@@ -4845,7 +4809,7 @@
         <v>16</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F103" s="4" t="s">
         <v>31</v>
@@ -4860,7 +4824,7 @@
         <v>20</v>
       </c>
       <c r="J103" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K103" s="3"/>
       <c r="L103" s="4" t="s">
@@ -4869,11 +4833,11 @@
     </row>
     <row r="104">
       <c r="A104" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B104" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="B104" s="3" t="s">
-        <v>215</v>
-      </c>
       <c r="C104" s="3" t="s">
         <v>15</v>
       </c>
@@ -4881,7 +4845,7 @@
         <v>16</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="F104" s="4" t="s">
         <v>25</v>
@@ -4896,7 +4860,7 @@
         <v>20</v>
       </c>
       <c r="J104" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="K104" s="3"/>
       <c r="L104" s="4" t="s">
@@ -4905,11 +4869,11 @@
     </row>
     <row r="105">
       <c r="A105" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B105" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="B105" s="3" t="s">
-        <v>219</v>
-      </c>
       <c r="C105" s="3" t="s">
         <v>15</v>
       </c>
@@ -4917,10 +4881,10 @@
         <v>16</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G105" s="4">
         <v>480</v>
@@ -4941,11 +4905,11 @@
     </row>
     <row r="106">
       <c r="A106" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B106" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="B106" s="3" t="s">
-        <v>219</v>
-      </c>
       <c r="C106" s="3" t="s">
         <v>15</v>
       </c>
@@ -4953,10 +4917,10 @@
         <v>16</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="G106" s="4">
         <v>480</v>
@@ -4977,10 +4941,10 @@
     </row>
     <row r="107">
       <c r="A107" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B107" s="3" t="s">
         <v>220</v>
-      </c>
-      <c r="B107" s="3" t="s">
-        <v>221</v>
       </c>
       <c r="C107" s="3" t="s">
         <v>15</v>
@@ -5004,7 +4968,7 @@
         <v>20</v>
       </c>
       <c r="J107" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="K107" s="3"/>
       <c r="L107" s="4" t="s">
@@ -5013,11 +4977,11 @@
     </row>
     <row r="108">
       <c r="A108" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B108" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="B108" s="3" t="s">
-        <v>221</v>
-      </c>
       <c r="C108" s="3" t="s">
         <v>15</v>
       </c>
@@ -5025,10 +4989,10 @@
         <v>16</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F108" s="4" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="G108" s="4">
         <v>480</v>
@@ -5040,7 +5004,7 @@
         <v>20</v>
       </c>
       <c r="J108" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="K108" s="3"/>
       <c r="L108" s="4" t="s">
@@ -5049,10 +5013,10 @@
     </row>
     <row r="109">
       <c r="A109" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B109" s="3" t="s">
         <v>224</v>
-      </c>
-      <c r="B109" s="3" t="s">
-        <v>225</v>
       </c>
       <c r="C109" s="3" t="s">
         <v>15</v>
@@ -5076,7 +5040,7 @@
         <v>20</v>
       </c>
       <c r="J109" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="K109" s="3"/>
       <c r="L109" s="4" t="s">
@@ -5085,11 +5049,11 @@
     </row>
     <row r="110">
       <c r="A110" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="B110" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="B110" s="3" t="s">
-        <v>228</v>
-      </c>
       <c r="C110" s="3" t="s">
         <v>15</v>
       </c>
@@ -5097,10 +5061,10 @@
         <v>16</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>168</v>
+        <v>55</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="G110" s="4">
         <v>90</v>
@@ -5112,7 +5076,7 @@
         <v>20</v>
       </c>
       <c r="J110" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="K110" s="3"/>
       <c r="L110" s="4" t="s">
@@ -5121,10 +5085,10 @@
     </row>
     <row r="111">
       <c r="A111" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="B111" s="3" t="s">
         <v>227</v>
-      </c>
-      <c r="B111" s="3" t="s">
-        <v>228</v>
       </c>
       <c r="C111" s="3" t="s">
         <v>15</v>
@@ -5139,7 +5103,7 @@
         <v>18</v>
       </c>
       <c r="G111" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H111" s="3" t="s">
         <v>19</v>
@@ -5148,7 +5112,7 @@
         <v>20</v>
       </c>
       <c r="J111" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K111" s="3"/>
       <c r="L111" s="4" t="s">
@@ -5157,10 +5121,10 @@
     </row>
     <row r="112">
       <c r="A112" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="B112" s="3" t="s">
         <v>227</v>
-      </c>
-      <c r="B112" s="3" t="s">
-        <v>228</v>
       </c>
       <c r="C112" s="3" t="s">
         <v>15</v>
@@ -5175,7 +5139,7 @@
         <v>29</v>
       </c>
       <c r="G112" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H112" s="3" t="s">
         <v>19</v>
@@ -5184,7 +5148,7 @@
         <v>20</v>
       </c>
       <c r="J112" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K112" s="3"/>
       <c r="L112" s="4" t="s">
@@ -5193,11 +5157,11 @@
     </row>
     <row r="113">
       <c r="A113" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="B113" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="B113" s="3" t="s">
-        <v>228</v>
-      </c>
       <c r="C113" s="3" t="s">
         <v>15</v>
       </c>
@@ -5205,10 +5169,10 @@
         <v>16</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>170</v>
+        <v>193</v>
       </c>
       <c r="F113" s="4" t="s">
-        <v>171</v>
+        <v>194</v>
       </c>
       <c r="G113" s="4">
         <v>90</v>
@@ -5220,7 +5184,7 @@
         <v>20</v>
       </c>
       <c r="J113" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K113" s="3"/>
       <c r="L113" s="4" t="s">
@@ -5229,34 +5193,34 @@
     </row>
     <row r="114">
       <c r="A114" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="B114" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="B114" s="3" t="s">
+      <c r="C114" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D114" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E114" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="F114" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="G114" s="4">
+        <v>90</v>
+      </c>
+      <c r="H114" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I114" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J114" s="3" t="s">
         <v>228</v>
-      </c>
-      <c r="C114" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D114" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E114" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F114" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="G114" s="4">
-        <v>480</v>
-      </c>
-      <c r="H114" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="I114" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J114" s="3" t="s">
-        <v>230</v>
       </c>
       <c r="K114" s="3"/>
       <c r="L114" s="4" t="s">
@@ -5265,11 +5229,11 @@
     </row>
     <row r="115">
       <c r="A115" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="B115" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="B115" s="3" t="s">
-        <v>228</v>
-      </c>
       <c r="C115" s="3" t="s">
         <v>15</v>
       </c>
@@ -5277,13 +5241,13 @@
         <v>16</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>174</v>
+        <v>36</v>
       </c>
       <c r="G115" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H115" s="3" t="s">
         <v>19</v>
@@ -5292,7 +5256,7 @@
         <v>20</v>
       </c>
       <c r="J115" s="3" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="K115" s="3"/>
       <c r="L115" s="4" t="s">
@@ -5301,11 +5265,11 @@
     </row>
     <row r="116">
       <c r="A116" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="B116" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="B116" s="3" t="s">
-        <v>228</v>
-      </c>
       <c r="C116" s="3" t="s">
         <v>15</v>
       </c>
@@ -5313,10 +5277,10 @@
         <v>16</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F116" s="4" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="G116" s="4">
         <v>90</v>
@@ -5328,7 +5292,7 @@
         <v>20</v>
       </c>
       <c r="J116" s="3" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="K116" s="3"/>
       <c r="L116" s="4" t="s">
@@ -5337,11 +5301,11 @@
     </row>
     <row r="117">
       <c r="A117" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="B117" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="B117" s="3" t="s">
-        <v>228</v>
-      </c>
       <c r="C117" s="3" t="s">
         <v>15</v>
       </c>
@@ -5349,10 +5313,10 @@
         <v>16</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="F117" s="4" t="s">
-        <v>166</v>
+        <v>205</v>
       </c>
       <c r="G117" s="4">
         <v>90</v>
@@ -5364,7 +5328,7 @@
         <v>20</v>
       </c>
       <c r="J117" s="3" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K117" s="3"/>
       <c r="L117" s="4" t="s">
@@ -5373,11 +5337,11 @@
     </row>
     <row r="118">
       <c r="A118" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="B118" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="B118" s="3" t="s">
-        <v>228</v>
-      </c>
       <c r="C118" s="3" t="s">
         <v>15</v>
       </c>
@@ -5385,10 +5349,10 @@
         <v>16</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F118" s="4" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="G118" s="4">
         <v>90</v>
@@ -5400,83 +5364,11 @@
         <v>20</v>
       </c>
       <c r="J118" s="3" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="K118" s="3"/>
       <c r="L118" s="4" t="s">
         <v>22</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="B119" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="C119" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D119" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E119" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="F119" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="G119" s="4">
-        <v>90</v>
-      </c>
-      <c r="H119" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="I119" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J119" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="K119" s="3"/>
-      <c r="L119" s="4" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="B120" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="C120" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D120" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E120" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="F120" s="4" t="s">
-        <v>248</v>
-      </c>
-      <c r="G120" s="4">
-        <v>90</v>
-      </c>
-      <c r="H120" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="I120" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J120" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="K120" s="3"/>
-      <c r="L120" s="4" t="s">
-        <v>244</v>
       </c>
     </row>
   </sheetData>
